--- a/docentes/Marin Arzaba Roberto - Estadisticos 20241.xlsx
+++ b/docentes/Marin Arzaba Roberto - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
   </si>
 </sst>
 </file>
@@ -661,16 +652,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -684,16 +678,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -707,16 +704,19 @@
         <v>28</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>28</v>
       </c>
-      <c r="E4">
-        <v>28</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -730,16 +730,19 @@
         <v>21</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -753,16 +756,19 @@
         <v>28</v>
       </c>
       <c r="D6">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>96.43000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -818,16 +824,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -853,7 +859,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -870,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>92.86</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -905,7 +911,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -922,16 +928,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>92.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -941,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -971,29 +977,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920232</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Marin Arzaba Roberto - Estadisticos 20241.xlsx
+++ b/docentes/Marin Arzaba Roberto - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
+    <t>JOSUE GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -532,10 +541,10 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -544,7 +553,7 @@
         <v>26</v>
       </c>
       <c r="G4">
-        <v>92.86</v>
+        <v>89.66</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -558,10 +567,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -570,7 +579,7 @@
         <v>20</v>
       </c>
       <c r="G5">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -701,10 +710,10 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -713,7 +722,7 @@
         <v>28</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>96.55</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -727,10 +736,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -739,7 +748,7 @@
         <v>20</v>
       </c>
       <c r="G5">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
         <v>7.8</v>
@@ -870,10 +879,10 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -882,7 +891,7 @@
         <v>28</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>96.55</v>
       </c>
       <c r="H4">
         <v>7.6</v>
@@ -896,10 +905,10 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -908,7 +917,7 @@
         <v>20</v>
       </c>
       <c r="G5">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H5">
         <v>7.5</v>
@@ -947,7 +956,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -977,6 +986,29 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920356</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Marin Arzaba Roberto - Estadisticos 20241.xlsx
+++ b/docentes/Marin Arzaba Roberto - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>JOSUE GUSTAVO</t>
   </si>
 </sst>
 </file>
@@ -842,7 +833,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -894,7 +885,7 @@
         <v>96.55</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -911,16 +902,16 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>90.91</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -937,16 +928,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>96.43000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +947,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -986,29 +977,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920356</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Marin Arzaba Roberto - Estadisticos 20241.xlsx
+++ b/docentes/Marin Arzaba Roberto - Estadisticos 20241.xlsx
@@ -535,19 +535,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>89.66</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -561,19 +561,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>90.91</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -704,19 +704,19 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>96.55</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -730,19 +730,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>90.91</v>
+        <v>95.45</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -873,16 +873,16 @@
         <v>29</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>96.55</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>8</v>
@@ -899,19 +899,19 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>95.45</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
